--- a/docs/SMPS_calc.xlsx
+++ b/docs/SMPS_calc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\seth\Documents\Git\cc-led-driver\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A457B39B-4E19-487B-8157-23DA4C3E3237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1F72F2-E8B0-4ADD-89D2-F19B12D7EF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" xr2:uid="{D66E1EC0-9458-49F0-B9B5-31025FA3405A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D66E1EC0-9458-49F0-B9B5-31025FA3405A}"/>
   </bookViews>
   <sheets>
     <sheet name="Buck" sheetId="2" r:id="rId1"/>
@@ -606,8 +606,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="##0.00E+0"/>
+    <numFmt numFmtId="165" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -666,7 +667,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -704,6 +705,9 @@
     <xf numFmtId="48" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2775,7 +2779,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.73509933774834435</c:v>
+                  <c:v>0.86559999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2787,10 +2791,10 @@
                 <c:formatCode>##0.0E+0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.63248344370860932</c:v>
+                  <c:v>-10.379759523809524</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.87751655629139069</c:v>
+                  <c:v>10.394640476190476</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2839,7 +2843,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.73509933774834435</c:v>
+                  <c:v>0.86559999999999993</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -2854,10 +2858,10 @@
                 <c:formatCode>##0.0E+0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.87751655629139069</c:v>
+                  <c:v>10.394640476190476</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.63248344370860932</c:v>
+                  <c:v>-10.379759523809524</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2910,10 +2914,10 @@
                 <c:formatCode>##0.0E+0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.755</c:v>
+                  <c:v>7.4404761904761901E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.755</c:v>
+                  <c:v>7.4404761904761901E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3386,7 +3390,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.8248287590894663</c:v>
+                  <c:v>2.3166923602549155E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3401,7 +3405,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.60827625302982213</c:v>
+                  <c:v>0.55600616646117973</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3450,10 +3454,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.8248287590894663</c:v>
+                  <c:v>2.3166923602549155E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4824247083108957</c:v>
+                  <c:v>2.6764006010338674E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3465,7 +3469,7 @@
                 <c:formatCode>##0.0E+0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.60827625302982213</c:v>
+                  <c:v>0.55600616646117973</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -3517,7 +3521,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2.4824247083108957</c:v>
+                  <c:v>2.6764006010338674E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -3588,10 +3592,10 @@
                 <c:formatCode>##0.0E+0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.755</c:v>
+                  <c:v>7.4404761904761901E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.755</c:v>
+                  <c:v>7.4404761904761901E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7354,18 +7358,18 @@
       <c r="B7" s="4">
         <v>0.9</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="H7" s="17" t="s">
+      <c r="F7" s="18"/>
+      <c r="H7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="17"/>
-      <c r="K7" s="17" t="s">
+      <c r="I7" s="18"/>
+      <c r="K7" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="17"/>
+      <c r="L7" s="18"/>
       <c r="O7" s="12"/>
       <c r="P7" s="12" t="s">
         <v>10</v>
@@ -7439,10 +7443,10 @@
       <c r="AA8" s="12"/>
     </row>
     <row r="9" spans="1:27" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="17"/>
+      <c r="B9" s="18"/>
       <c r="E9" s="4">
         <v>0</v>
       </c>
@@ -7670,10 +7674,10 @@
       <c r="AA15" s="12"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="17"/>
+      <c r="B16" s="18"/>
       <c r="O16" s="12"/>
       <c r="P16" s="12"/>
       <c r="Q16" s="12"/>
@@ -7923,19 +7927,19 @@
       <c r="AA28" s="12"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="H29" s="17" t="s">
+      <c r="F29" s="18"/>
+      <c r="H29" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I29" s="17"/>
+      <c r="I29" s="18"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="17"/>
+      <c r="L29" s="18"/>
       <c r="O29" s="12"/>
       <c r="P29" s="12"/>
       <c r="Q29" s="12"/>
@@ -8286,7 +8290,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="5">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="18" x14ac:dyDescent="0.35">
@@ -8294,7 +8298,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="5">
-        <v>15.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8302,7 +8306,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="5">
-        <v>0.2</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8310,7 +8314,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="5">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
@@ -8318,7 +8322,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="5">
-        <v>1.5E-5</v>
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="18" x14ac:dyDescent="0.35">
@@ -8326,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="4">
-        <v>0.8</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -8337,12 +8341,16 @@
       <c r="K7" t="s">
         <v>18</v>
       </c>
+      <c r="N7" s="6">
+        <f>AC7</f>
+        <v>7.4404761904761901E-3</v>
+      </c>
       <c r="AB7" s="1" t="s">
         <v>34</v>
       </c>
       <c r="AC7" s="6">
         <f>(B3*B4)/(B2*B7)</f>
-        <v>0.755</v>
+        <v>7.4404761904761901E-3</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -8366,31 +8374,31 @@
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="17"/>
+      <c r="B9" s="18"/>
       <c r="E9" s="4">
         <v>0</v>
       </c>
       <c r="F9" s="5">
         <f>B13</f>
-        <v>0.63248344370860932</v>
+        <v>-10.379759523809524</v>
       </c>
       <c r="H9" s="2">
         <f>B10</f>
-        <v>0.73509933774834435</v>
+        <v>0.86559999999999993</v>
       </c>
       <c r="I9" s="6">
         <f>B12</f>
-        <v>0.87751655629139069</v>
+        <v>10.394640476190476</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
       </c>
       <c r="L9" s="6">
         <f>AC7</f>
-        <v>0.755</v>
+        <v>7.4404761904761901E-3</v>
       </c>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
@@ -8399,29 +8407,29 @@
       </c>
       <c r="B10" s="4">
         <f>1-(B2*B7)/B3</f>
-        <v>0.73509933774834435</v>
+        <v>0.86559999999999993</v>
       </c>
       <c r="E10" s="4">
         <f>B10</f>
-        <v>0.73509933774834435</v>
+        <v>0.86559999999999993</v>
       </c>
       <c r="F10" s="5">
         <f>B12</f>
-        <v>0.87751655629139069</v>
+        <v>10.394640476190476</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
       </c>
       <c r="I10" s="6">
         <f>B13</f>
-        <v>0.63248344370860932</v>
+        <v>-10.379759523809524</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
       </c>
       <c r="L10" s="6">
         <f>AC7</f>
-        <v>0.755</v>
+        <v>7.4404761904761901E-3</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="18" x14ac:dyDescent="0.35">
@@ -8430,7 +8438,7 @@
       </c>
       <c r="B11" s="5">
         <f>(B2*B10)/(B6*B5)</f>
-        <v>0.24503311258278146</v>
+        <v>20.7744</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8439,7 +8447,7 @@
       </c>
       <c r="B12" s="9">
         <f>B11/2+AC7</f>
-        <v>0.87751655629139069</v>
+        <v>10.394640476190476</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="18" x14ac:dyDescent="0.35">
@@ -8448,7 +8456,7 @@
       </c>
       <c r="B13" s="8">
         <f>AC7-B11/2</f>
-        <v>0.63248344370860932</v>
+        <v>-10.379759523809524</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="18" x14ac:dyDescent="0.35">
@@ -8457,14 +8465,14 @@
       </c>
       <c r="B14" s="9">
         <f>SQRT(((B12)^2+(B13)^2+(B12*B13))/3)</f>
-        <v>0.75830629400119964</v>
+        <v>5.9970573317824751</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="17"/>
+      <c r="B16" s="18"/>
     </row>
     <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -8472,25 +8480,25 @@
       </c>
       <c r="B17" s="4">
         <f>(2*B4*B3*B6*B5)/(B2^2*B7)</f>
-        <v>4.53</v>
+        <v>6.2003968253968251E-4</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="17">
         <f>(SQRT((AC7*2*B6)/(B5*B2*B10))/(1/B5))</f>
-        <v>2.4824247083108957</v>
+        <v>2.6764006010338674E-2</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="17">
         <f>B18*B10</f>
-        <v>1.8248287590894663</v>
+        <v>2.3166923602549155E-2</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="18" x14ac:dyDescent="0.35">
@@ -8499,7 +8507,7 @@
       </c>
       <c r="B20" s="5">
         <f>(B2*B19)/(B6*B5)</f>
-        <v>0.60827625302982213</v>
+        <v>0.55600616646117973</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="18" x14ac:dyDescent="0.35">
@@ -8508,7 +8516,7 @@
       </c>
       <c r="B21" s="9">
         <f>B20</f>
-        <v>0.60827625302982213</v>
+        <v>0.55600616646117973</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="18" x14ac:dyDescent="0.35">
@@ -8526,19 +8534,19 @@
       </c>
       <c r="B23" s="9">
         <f>B21*SQRT(B18/3)</f>
-        <v>0.55332243224453737</v>
+        <v>5.251635074471156E-2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="I29" s="17"/>
+      <c r="I29" s="18"/>
       <c r="J29" s="4"/>
-      <c r="K29" s="17" t="s">
+      <c r="K29" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="17"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H30" s="3" t="s">
@@ -8566,26 +8574,26 @@
       <c r="J31" s="3"/>
       <c r="K31" s="7">
         <f>B19</f>
-        <v>1.8248287590894663</v>
+        <v>2.3166923602549155E-2</v>
       </c>
       <c r="L31" s="5">
         <f>B21</f>
-        <v>0.60827625302982213</v>
+        <v>0.55600616646117973</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H32" s="4">
         <f>B19</f>
-        <v>1.8248287590894663</v>
+        <v>2.3166923602549155E-2</v>
       </c>
       <c r="I32" s="5">
         <f>B21</f>
-        <v>0.60827625302982213</v>
+        <v>0.55600616646117973</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="7">
         <f>B18</f>
-        <v>2.4824247083108957</v>
+        <v>2.6764006010338674E-2</v>
       </c>
       <c r="L32" s="5">
         <f>B22</f>
@@ -8600,10 +8608,10 @@
       <c r="L33" s="3"/>
     </row>
     <row r="34" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="17"/>
+      <c r="I34" s="18"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -8622,7 +8630,7 @@
     <row r="36" spans="8:12" x14ac:dyDescent="0.25">
       <c r="H36" s="4">
         <f>B18</f>
-        <v>2.4824247083108957</v>
+        <v>2.6764006010338674E-2</v>
       </c>
       <c r="I36" s="5">
         <f>B22</f>
